--- a/artfynd/A 26190-2024 artfynd.xlsx
+++ b/artfynd/A 26190-2024 artfynd.xlsx
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130637680</v>
+        <v>130637699</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,42 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733581</v>
+        <v>733505</v>
       </c>
       <c r="R6" t="n">
-        <v>7179336</v>
+        <v>7179505</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1165,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130637699</v>
+        <v>130637680</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1202,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733505</v>
+        <v>733581</v>
       </c>
       <c r="R7" t="n">
-        <v>7179505</v>
+        <v>7179336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 26190-2024 artfynd.xlsx
+++ b/artfynd/A 26190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130637697</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130637698</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130637683</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>130637681</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>130637699</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>130637680</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>130637682</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26190-2024 artfynd.xlsx
+++ b/artfynd/A 26190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130637697</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130637698</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130637683</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>130637681</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>130637699</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>130637680</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>130637682</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26190-2024 artfynd.xlsx
+++ b/artfynd/A 26190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130637697</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130637698</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130637683</v>
       </c>
       <c r="B4" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>130637681</v>
       </c>
       <c r="B5" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130637699</v>
+        <v>130637680</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,34 +1105,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733505</v>
+        <v>733581</v>
       </c>
       <c r="R6" t="n">
-        <v>7179505</v>
+        <v>7179336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130637680</v>
+        <v>130637699</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,42 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733581</v>
+        <v>733505</v>
       </c>
       <c r="R7" t="n">
-        <v>7179336</v>
+        <v>7179505</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>130637682</v>
       </c>
       <c r="B8" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26190-2024 artfynd.xlsx
+++ b/artfynd/A 26190-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130637697</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130637698</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130637683</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>130637681</v>
       </c>
       <c r="B5" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130637680</v>
+        <v>130637699</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,42 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733581</v>
+        <v>733505</v>
       </c>
       <c r="R6" t="n">
-        <v>7179336</v>
+        <v>7179505</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1165,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130637699</v>
+        <v>130637680</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1202,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733505</v>
+        <v>733581</v>
       </c>
       <c r="R7" t="n">
-        <v>7179505</v>
+        <v>7179336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>130637682</v>
       </c>
       <c r="B8" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 26190-2024 artfynd.xlsx
+++ b/artfynd/A 26190-2024 artfynd.xlsx
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130637699</v>
+        <v>130637680</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,34 +1105,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733505</v>
+        <v>733581</v>
       </c>
       <c r="R6" t="n">
-        <v>7179505</v>
+        <v>7179336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130637680</v>
+        <v>130637699</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,42 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733581</v>
+        <v>733505</v>
       </c>
       <c r="R7" t="n">
-        <v>7179336</v>
+        <v>7179505</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 26190-2024 artfynd.xlsx
+++ b/artfynd/A 26190-2024 artfynd.xlsx
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130637680</v>
+        <v>130637699</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,42 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733581</v>
+        <v>733505</v>
       </c>
       <c r="R6" t="n">
-        <v>7179336</v>
+        <v>7179505</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1165,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130637699</v>
+        <v>130637680</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1202,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733505</v>
+        <v>733581</v>
       </c>
       <c r="R7" t="n">
-        <v>7179505</v>
+        <v>7179336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack flera granar, färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
